--- a/artfynd/A 59198-2025 artfynd.xlsx
+++ b/artfynd/A 59198-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130021444</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59198-2025 artfynd.xlsx
+++ b/artfynd/A 59198-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130021444</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59198-2025 artfynd.xlsx
+++ b/artfynd/A 59198-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130021444</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59198-2025 artfynd.xlsx
+++ b/artfynd/A 59198-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130021444</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59198-2025 artfynd.xlsx
+++ b/artfynd/A 59198-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130021444</v>
+        <v>122744531</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1639</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 59198, Långsjön, Sm</t>
+          <t>Bykesbergen Ö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578303</v>
+        <v>578355</v>
       </c>
       <c r="R2" t="n">
-        <v>6396414</v>
+        <v>6396337</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På nedfallen gren i ekbestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,22 +759,989 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130021419</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91334</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödbrun jordstjärna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Geastrum rufescens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 59198, Långskjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>578315</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6396399</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130127278</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91334</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödbrun jordstjärna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Geastrum rufescens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 59198, Långsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578315</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6396398</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122744533</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96501</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Simonstorp V, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>578255</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6396359</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130021519</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 59198, Långsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>578280</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6396402</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122744535</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92031</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Axtorpet N, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>578259</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6396392</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På grov asplåga</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122744532</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91932</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rodga N, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>578252</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6396348</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130021352</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 59198, Långsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578328</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6396364</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134460821</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 59198, Långsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>578290</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6396401</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130021444</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 59198, Långsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578303</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6396414</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
